--- a/trading_signals/risk_management/risk_workbook_20260624_000000.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260624_000000.xlsx
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-23  ·  Generated 2026-06-24T21:39:42  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-23  ·  Generated 2026-06-25T01:51:03  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
         <v>1087</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>2304436</v>
+        <v>2304435</v>
       </c>
       <c r="E7" s="17" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>56</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3205792</v>
+        <v>3196982</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
         <v>874</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1505640</v>
+        <v>1435760</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
@@ -1386,7 +1386,7 @@
         <v>177</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>9346875</v>
+        <v>9346880</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
@@ -1428,7 +1428,7 @@
         <v>187</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4719808</v>
+        <v>4719809</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
@@ -1470,7 +1470,7 @@
         <v>177</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>9346875</v>
+        <v>9346880</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>0</v>
